--- a/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
+++ b/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
@@ -517,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -658,6 +658,18 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -985,14 +997,6 @@
           <t>THORNFIELD LIFE SCIENCES MARKETING</t>
         </is>
       </c>
-      <c r="B1" s="17" t="n"/>
-      <c r="C1" s="17" t="n"/>
-      <c r="D1" s="17" t="n"/>
-      <c r="E1" s="17" t="n"/>
-      <c r="F1" s="17" t="n"/>
-      <c r="G1" s="17" t="n"/>
-      <c r="H1" s="17" t="n"/>
-      <c r="I1" s="17" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
@@ -1000,51 +1004,36 @@
           <t>Creative Brief Doc-Control Log</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="18" t="n"/>
-      <c r="H2" s="18" t="n"/>
-      <c r="I2" s="18" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>Authoritative approval register for creative briefs and campaign deliverables produced by the Thornfield Creative team. Per the Document Version-Control &amp; Approval Policy (A24, 10/01/2025), the approval status recorded in this log — not the filename, not the modification date, and not the last message in a chat thread — is the sole authoritative signal of which version is approved for use. Any deliverable not listed here with a matching version identifier and an APPROVED status is not approved. Superseded rows are retained for audit history and are not overwritten.</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="n"/>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
-      <c r="I3" s="21" t="n"/>
+      <c r="A3" s="54" t="inlineStr">
+        <is>
+          <t>Authoritative approval register for creative briefs and campaign deliverables produced by the Thornfield Creative team. Per the Document Version-Control &amp; Approval Policy (effective 10/01/2025), the approval status recorded in this log — not the filename, not the modification date, and not the last message in a chat thread — is the sole authoritative signal of which version is approved for use. Any deliverable not listed here with a matching version identifier and an APPROVED status is not approved. Superseded rows are retained for audit history and are not overwritten.</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="n"/>
+      <c r="C3" s="55" t="n"/>
+      <c r="D3" s="55" t="n"/>
+      <c r="E3" s="55" t="n"/>
+      <c r="F3" s="55" t="n"/>
+      <c r="G3" s="55" t="n"/>
+      <c r="H3" s="55" t="n"/>
+      <c r="I3" s="56" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="23" t="n"/>
-      <c r="C4" s="23" t="n"/>
-      <c r="D4" s="23" t="n"/>
-      <c r="E4" s="23" t="n"/>
-      <c r="F4" s="23" t="n"/>
-      <c r="G4" s="23" t="n"/>
-      <c r="H4" s="23" t="n"/>
-      <c r="I4" s="24" t="n"/>
+      <c r="A4" s="57" t="n"/>
+      <c r="I4" s="58" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="25" t="n"/>
-      <c r="B5" s="26" t="n"/>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="26" t="n"/>
-      <c r="F5" s="26" t="n"/>
-      <c r="G5" s="26" t="n"/>
-      <c r="H5" s="26" t="n"/>
-      <c r="I5" s="27" t="n"/>
+      <c r="A5" s="59" t="n"/>
+      <c r="B5" s="60" t="n"/>
+      <c r="C5" s="60" t="n"/>
+      <c r="D5" s="60" t="n"/>
+      <c r="E5" s="60" t="n"/>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="60" t="n"/>
+      <c r="H5" s="60" t="n"/>
+      <c r="I5" s="61" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="28" t="inlineStr">
@@ -1052,14 +1041,14 @@
           <t>Owner: Owen Castellano, Creative Director   |   Log location: /Creative/DocControl/creative_brief_doc_control_log.xlsx</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n"/>
-      <c r="C6" s="28" t="n"/>
-      <c r="D6" s="28" t="n"/>
-      <c r="E6" s="28" t="n"/>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="28" t="n"/>
-      <c r="H6" s="28" t="n"/>
-      <c r="I6" s="28" t="n"/>
+      <c r="B6" s="62" t="n"/>
+      <c r="C6" s="62" t="n"/>
+      <c r="D6" s="62" t="n"/>
+      <c r="E6" s="62" t="n"/>
+      <c r="F6" s="62" t="n"/>
+      <c r="G6" s="62" t="n"/>
+      <c r="H6" s="62" t="n"/>
+      <c r="I6" s="62" t="n"/>
     </row>
     <row r="7" ht="12" customHeight="1"/>
     <row r="8" ht="32" customHeight="1">
@@ -1963,14 +1952,14 @@
           <t>Log maintained by: Owen Castellano, Creative Director</t>
         </is>
       </c>
-      <c r="B29" s="49" t="n"/>
-      <c r="C29" s="49" t="n"/>
-      <c r="D29" s="49" t="n"/>
-      <c r="E29" s="49" t="n"/>
-      <c r="F29" s="49" t="n"/>
-      <c r="G29" s="49" t="n"/>
-      <c r="H29" s="49" t="n"/>
-      <c r="I29" s="49" t="n"/>
+      <c r="B29" s="63" t="n"/>
+      <c r="C29" s="63" t="n"/>
+      <c r="D29" s="63" t="n"/>
+      <c r="E29" s="63" t="n"/>
+      <c r="F29" s="63" t="n"/>
+      <c r="G29" s="63" t="n"/>
+      <c r="H29" s="63" t="n"/>
+      <c r="I29" s="63" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="51" t="inlineStr">
@@ -1978,14 +1967,6 @@
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="B30" s="51" t="n"/>
-      <c r="C30" s="51" t="n"/>
-      <c r="D30" s="51" t="n"/>
-      <c r="E30" s="51" t="n"/>
-      <c r="F30" s="51" t="n"/>
-      <c r="G30" s="51" t="n"/>
-      <c r="H30" s="51" t="n"/>
-      <c r="I30" s="51" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="52" t="inlineStr">
@@ -1993,14 +1974,6 @@
           <t>owen.castellano@thornfieldlsm.com</t>
         </is>
       </c>
-      <c r="B31" s="52" t="n"/>
-      <c r="C31" s="52" t="n"/>
-      <c r="D31" s="52" t="n"/>
-      <c r="E31" s="52" t="n"/>
-      <c r="F31" s="52" t="n"/>
-      <c r="G31" s="52" t="n"/>
-      <c r="H31" s="52" t="n"/>
-      <c r="I31" s="52" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="53" t="inlineStr">
@@ -2008,14 +1981,6 @@
           <t>Last updated: 12/28/2025</t>
         </is>
       </c>
-      <c r="B32" s="53" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
-      <c r="E32" s="53" t="n"/>
-      <c r="F32" s="53" t="n"/>
-      <c r="G32" s="53" t="n"/>
-      <c r="H32" s="53" t="n"/>
-      <c r="I32" s="53" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A8:I26"/>

--- a/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
+++ b/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -179,6 +179,12 @@
       <name val="Segoe UI"/>
       <i val="1"/>
       <color rgb="0094A3B8"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF334155"/>
       <sz val="8.5"/>
     </font>
   </fonts>
@@ -262,7 +268,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -513,11 +519,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -670,6 +692,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1036,7 +1067,7 @@
       <c r="I5" s="61" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>Owner: Owen Castellano, Creative Director   |   Log location: /Creative/DocControl/creative_brief_doc_control_log.xlsx</t>
         </is>
@@ -1947,7 +1978,7 @@
     <row r="27" ht="12" customHeight="1"/>
     <row r="28" ht="12" customHeight="1"/>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="49" t="inlineStr">
+      <c r="A29" s="65" t="inlineStr">
         <is>
           <t>Log maintained by: Owen Castellano, Creative Director</t>
         </is>
@@ -1976,7 +2007,7 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="53" t="inlineStr">
+      <c r="A32" s="66" t="inlineStr">
         <is>
           <t>Last updated: 12/28/2025</t>
         </is>

--- a/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
+++ b/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
@@ -539,7 +539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -699,6 +699,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1105,7 +1108,7 @@
       </c>
       <c r="E8" s="31" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Filename (Creative Cloud Library)</t>
         </is>
       </c>
       <c r="F8" s="31" t="inlineStr">
@@ -1975,7 +1978,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="12" customHeight="1"/>
+    <row r="27" ht="12" customHeight="1">
+      <c r="A27" s="67" t="inlineStr">
+        <is>
+          <t>Brief source files (.docx) referenced above are stored in Thornfield's Creative Cloud library, not in this MarketingOps file-system tree; this log is the authoritative index of version, approval status, and audit history for each brief.</t>
+        </is>
+      </c>
+    </row>
     <row r="28" ht="12" customHeight="1"/>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="65" t="inlineStr">
@@ -2015,11 +2024,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A8:I26"/>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A3:I5"/>

--- a/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
+++ b/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E8" s="31" t="inlineStr">
         <is>
-          <t>Filename (Creative Cloud Library)</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="F8" s="31" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="27" ht="12" customHeight="1">
       <c r="A27" s="67" t="inlineStr">
         <is>
-          <t>Brief source files (.docx) referenced above are stored in Thornfield's Creative Cloud library, not in this MarketingOps file-system tree; this log is the authoritative index of version, approval status, and audit history for each brief.</t>
+          <t>Brief source files (.docx) referenced above are retained in Thornfield's Creative Cloud library, not in this MarketingOps file-system tree, with one exception: the current APPROVED, authoritative brief for the Caldwell Diagnostics — Q1 2026 Assay Launch campaign (LOG-2025-0114, filename Brief_v1.3.docx) is mirrored at /Creative/Briefs/Caldwell/Brief_v1.3.docx alongside this log. This log remains the authoritative index of version, approval status, and audit history for every brief.</t>
         </is>
       </c>
     </row>

--- a/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
+++ b/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E8" s="31" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Filename (Creative Cloud Library)</t>
         </is>
       </c>
       <c r="F8" s="31" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="27" ht="12" customHeight="1">
       <c r="A27" s="67" t="inlineStr">
         <is>
-          <t>Brief source files (.docx) referenced above are retained in Thornfield's Creative Cloud library, not in this MarketingOps file-system tree, with one exception: the current APPROVED, authoritative brief for the Caldwell Diagnostics — Q1 2026 Assay Launch campaign (LOG-2025-0114, filename Brief_v1.3.docx) is mirrored at /Creative/Briefs/Caldwell/Brief_v1.3.docx alongside this log. This log remains the authoritative index of version, approval status, and audit history for every brief.</t>
+          <t>Brief source files (.docx) referenced above are stored in Thornfield's Creative Cloud library, not in this MarketingOps file-system tree; this log is the authoritative index of version, approval status, and audit history for each brief.</t>
         </is>
       </c>
     </row>

--- a/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
+++ b/filesystem/Creative/DocControl/creative_brief_doc_control_log.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -186,6 +186,27 @@
       <i val="1"/>
       <color rgb="FF334155"/>
       <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1E40AF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="FF1E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF1E40AF"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="14">
@@ -539,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -702,6 +723,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1026,7 +1062,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>THORNFIELD LIFE SCIENCES MARKETING</t>
         </is>
@@ -1153,7 +1189,7 @@
           <t>v1.1</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="E9" s="69" t="inlineStr">
         <is>
           <t>Brief_v1.1.docx</t>
         </is>
@@ -1200,7 +1236,7 @@
           <t>v2.0</t>
         </is>
       </c>
-      <c r="E10" s="44" t="inlineStr">
+      <c r="E10" s="70" t="inlineStr">
         <is>
           <t>Brief_v2.0.docx</t>
         </is>
@@ -1247,7 +1283,7 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="E11" s="69" t="inlineStr">
         <is>
           <t>Brief_v1.0.docx</t>
         </is>
@@ -1294,7 +1330,7 @@
           <t>v1.2</t>
         </is>
       </c>
-      <c r="E12" s="44" t="inlineStr">
+      <c r="E12" s="70" t="inlineStr">
         <is>
           <t>Brief_v1.2.docx</t>
         </is>
@@ -1341,7 +1377,7 @@
           <t>v1.4</t>
         </is>
       </c>
-      <c r="E13" s="36" t="inlineStr">
+      <c r="E13" s="69" t="inlineStr">
         <is>
           <t>Brief_v1.4.docx</t>
         </is>
@@ -1388,7 +1424,7 @@
           <t>v1.1</t>
         </is>
       </c>
-      <c r="E14" s="44" t="inlineStr">
+      <c r="E14" s="70" t="inlineStr">
         <is>
           <t>Brief_v1.1.docx</t>
         </is>
@@ -1435,7 +1471,7 @@
           <t>v0.5</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
+      <c r="E15" s="69" t="inlineStr">
         <is>
           <t>Brief_v0.5.docx</t>
         </is>
@@ -1482,7 +1518,7 @@
           <t>v2.1</t>
         </is>
       </c>
-      <c r="E16" s="44" t="inlineStr">
+      <c r="E16" s="70" t="inlineStr">
         <is>
           <t>Brief_v2.1.docx</t>
         </is>
@@ -1529,7 +1565,7 @@
           <t>v1.1</t>
         </is>
       </c>
-      <c r="E17" s="36" t="inlineStr">
+      <c r="E17" s="69" t="inlineStr">
         <is>
           <t>Brief_v1.1.docx</t>
         </is>
@@ -1576,7 +1612,7 @@
           <t>v0.9</t>
         </is>
       </c>
-      <c r="E18" s="44" t="inlineStr">
+      <c r="E18" s="70" t="inlineStr">
         <is>
           <t>Brief_v0.9.docx</t>
         </is>
@@ -1623,7 +1659,7 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E19" s="69" t="inlineStr">
         <is>
           <t>Brief_v1.0.docx</t>
         </is>
@@ -1670,7 +1706,7 @@
           <t>v1.5</t>
         </is>
       </c>
-      <c r="E20" s="44" t="inlineStr">
+      <c r="E20" s="70" t="inlineStr">
         <is>
           <t>Brief_v1.5.docx</t>
         </is>
@@ -1717,7 +1753,7 @@
           <t>v1.2</t>
         </is>
       </c>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="E21" s="69" t="inlineStr">
         <is>
           <t>Brief_v1.2.docx</t>
         </is>
@@ -1764,7 +1800,7 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="E22" s="44" t="inlineStr">
+      <c r="E22" s="70" t="inlineStr">
         <is>
           <t>Brief_v1.3.docx</t>
         </is>
@@ -1811,7 +1847,7 @@
           <t>v1.1</t>
         </is>
       </c>
-      <c r="E23" s="36" t="inlineStr">
+      <c r="E23" s="69" t="inlineStr">
         <is>
           <t>Brief_v1.1.docx</t>
         </is>
@@ -1858,7 +1894,7 @@
           <t>v1.2</t>
         </is>
       </c>
-      <c r="E24" s="44" t="inlineStr">
+      <c r="E24" s="70" t="inlineStr">
         <is>
           <t>Brief_v1.2.docx</t>
         </is>
@@ -1905,7 +1941,7 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="E25" s="36" t="inlineStr">
+      <c r="E25" s="69" t="inlineStr">
         <is>
           <t>Brief_v1.3.docx</t>
         </is>
@@ -1952,7 +1988,7 @@
           <t>v1.2</t>
         </is>
       </c>
-      <c r="E26" s="44" t="inlineStr">
+      <c r="E26" s="70" t="inlineStr">
         <is>
           <t>Brief_v1.2.docx</t>
         </is>
@@ -2002,14 +2038,14 @@
       <c r="I29" s="63" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="51" t="inlineStr">
+      <c r="A30" s="71" t="inlineStr">
         <is>
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="52" t="inlineStr">
+      <c r="A31" s="72" t="inlineStr">
         <is>
           <t>owen.castellano@thornfieldlsm.com</t>
         </is>
